--- a/AC_2010Bye/AC_031_Huzurabad.xlsx
+++ b/AC_2010Bye/AC_031_Huzurabad.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,8 +45,14 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -59,8 +65,26 @@
         <bgColor rgb="001F497D"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -82,11 +106,53 @@
         <color rgb="00D9D9D9"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="medium">
+        <color rgb="001B365D"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D3D3D3"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D3D3D3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D3D3D3"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D3D3D3"/>
+      </top>
+      <bottom style="double">
+        <color rgb="001B365D"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -102,6 +168,19 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -468,7 +547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BX279"/>
+  <dimension ref="A1:BX281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -570,6 +649,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
@@ -64318,301 +64398,840 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="6" t="inlineStr">
+      <c r="A279" s="8" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>TOTAL EVM VOTES</t>
         </is>
       </c>
-      <c r="C279" s="7">
+      <c r="B279" s="13" t="inlineStr"/>
+      <c r="C279" s="14">
         <f>SUM(C6:C278)</f>
         <v/>
       </c>
-      <c r="D279" s="7">
+      <c r="D279" s="14">
         <f>SUM(D6:D278)</f>
         <v/>
       </c>
-      <c r="E279" s="7">
+      <c r="E279" s="14">
         <f>SUM(E6:E278)</f>
         <v/>
       </c>
-      <c r="F279" s="7">
+      <c r="F279" s="14">
         <f>SUM(F6:F278)</f>
         <v/>
       </c>
-      <c r="G279" s="7">
+      <c r="G279" s="14">
         <f>SUM(G6:G278)</f>
         <v/>
       </c>
-      <c r="H279" s="7">
+      <c r="H279" s="14">
         <f>SUM(H6:H278)</f>
         <v/>
       </c>
-      <c r="I279" s="7">
+      <c r="I279" s="14">
         <f>SUM(I6:I278)</f>
         <v/>
       </c>
-      <c r="J279" s="7">
+      <c r="J279" s="14">
         <f>SUM(J6:J278)</f>
         <v/>
       </c>
-      <c r="K279" s="7">
+      <c r="K279" s="14">
         <f>SUM(K6:K278)</f>
         <v/>
       </c>
-      <c r="L279" s="7">
+      <c r="L279" s="14">
         <f>SUM(L6:L278)</f>
         <v/>
       </c>
-      <c r="M279" s="7">
+      <c r="M279" s="14">
         <f>SUM(M6:M278)</f>
         <v/>
       </c>
-      <c r="N279" s="7">
+      <c r="N279" s="14">
         <f>SUM(N6:N278)</f>
         <v/>
       </c>
-      <c r="O279" s="7">
+      <c r="O279" s="14">
         <f>SUM(O6:O278)</f>
         <v/>
       </c>
-      <c r="P279" s="7">
+      <c r="P279" s="14">
         <f>SUM(P6:P278)</f>
         <v/>
       </c>
-      <c r="Q279" s="7">
+      <c r="Q279" s="14">
         <f>SUM(Q6:Q278)</f>
         <v/>
       </c>
-      <c r="R279" s="7">
+      <c r="R279" s="14">
         <f>SUM(R6:R278)</f>
         <v/>
       </c>
-      <c r="S279" s="7">
+      <c r="S279" s="14">
         <f>SUM(S6:S278)</f>
         <v/>
       </c>
-      <c r="T279" s="7">
+      <c r="T279" s="14">
         <f>SUM(T6:T278)</f>
         <v/>
       </c>
-      <c r="U279" s="7">
+      <c r="U279" s="14">
         <f>SUM(U6:U278)</f>
         <v/>
       </c>
-      <c r="V279" s="7">
+      <c r="V279" s="14">
         <f>SUM(V6:V278)</f>
         <v/>
       </c>
-      <c r="W279" s="7">
+      <c r="W279" s="14">
         <f>SUM(W6:W278)</f>
         <v/>
       </c>
-      <c r="X279" s="7">
+      <c r="X279" s="14">
         <f>SUM(X6:X278)</f>
         <v/>
       </c>
-      <c r="Y279" s="7">
+      <c r="Y279" s="14">
         <f>SUM(Y6:Y278)</f>
         <v/>
       </c>
-      <c r="Z279" s="7">
+      <c r="Z279" s="14">
         <f>SUM(Z6:Z278)</f>
         <v/>
       </c>
-      <c r="AA279" s="7">
+      <c r="AA279" s="14">
         <f>SUM(AA6:AA278)</f>
         <v/>
       </c>
-      <c r="AB279" s="7">
+      <c r="AB279" s="14">
         <f>SUM(AB6:AB278)</f>
         <v/>
       </c>
-      <c r="AC279" s="7">
+      <c r="AC279" s="14">
         <f>SUM(AC6:AC278)</f>
         <v/>
       </c>
-      <c r="AD279" s="7">
+      <c r="AD279" s="14">
         <f>SUM(AD6:AD278)</f>
         <v/>
       </c>
-      <c r="AE279" s="7">
+      <c r="AE279" s="14">
         <f>SUM(AE6:AE278)</f>
         <v/>
       </c>
-      <c r="AF279" s="7">
+      <c r="AF279" s="14">
         <f>SUM(AF6:AF278)</f>
         <v/>
       </c>
-      <c r="AG279" s="7">
+      <c r="AG279" s="14">
         <f>SUM(AG6:AG278)</f>
         <v/>
       </c>
-      <c r="AH279" s="7">
+      <c r="AH279" s="14">
         <f>SUM(AH6:AH278)</f>
         <v/>
       </c>
-      <c r="AI279" s="7">
+      <c r="AI279" s="14">
         <f>SUM(AI6:AI278)</f>
         <v/>
       </c>
-      <c r="AJ279" s="7">
+      <c r="AJ279" s="14">
         <f>SUM(AJ6:AJ278)</f>
         <v/>
       </c>
-      <c r="AK279" s="7">
+      <c r="AK279" s="14">
         <f>SUM(AK6:AK278)</f>
         <v/>
       </c>
-      <c r="AL279" s="7">
+      <c r="AL279" s="14">
         <f>SUM(AL6:AL278)</f>
         <v/>
       </c>
-      <c r="AM279" s="7">
+      <c r="AM279" s="14">
         <f>SUM(AM6:AM278)</f>
         <v/>
       </c>
-      <c r="AN279" s="7">
+      <c r="AN279" s="14">
         <f>SUM(AN6:AN278)</f>
         <v/>
       </c>
-      <c r="AO279" s="7">
+      <c r="AO279" s="14">
         <f>SUM(AO6:AO278)</f>
         <v/>
       </c>
-      <c r="AP279" s="7">
+      <c r="AP279" s="14">
         <f>SUM(AP6:AP278)</f>
         <v/>
       </c>
-      <c r="AQ279" s="7">
+      <c r="AQ279" s="14">
         <f>SUM(AQ6:AQ278)</f>
         <v/>
       </c>
-      <c r="AR279" s="7">
+      <c r="AR279" s="14">
         <f>SUM(AR6:AR278)</f>
         <v/>
       </c>
-      <c r="AS279" s="7">
+      <c r="AS279" s="14">
         <f>SUM(AS6:AS278)</f>
         <v/>
       </c>
-      <c r="AT279" s="7">
+      <c r="AT279" s="14">
         <f>SUM(AT6:AT278)</f>
         <v/>
       </c>
-      <c r="AU279" s="7">
+      <c r="AU279" s="14">
         <f>SUM(AU6:AU278)</f>
         <v/>
       </c>
-      <c r="AV279" s="7">
+      <c r="AV279" s="14">
         <f>SUM(AV6:AV278)</f>
         <v/>
       </c>
-      <c r="AW279" s="7">
+      <c r="AW279" s="14">
         <f>SUM(AW6:AW278)</f>
         <v/>
       </c>
-      <c r="AX279" s="7">
+      <c r="AX279" s="14">
         <f>SUM(AX6:AX278)</f>
         <v/>
       </c>
-      <c r="AY279" s="7">
+      <c r="AY279" s="14">
         <f>SUM(AY6:AY278)</f>
         <v/>
       </c>
-      <c r="AZ279" s="7">
+      <c r="AZ279" s="14">
         <f>SUM(AZ6:AZ278)</f>
         <v/>
       </c>
-      <c r="BA279" s="7">
+      <c r="BA279" s="14">
         <f>SUM(BA6:BA278)</f>
         <v/>
       </c>
-      <c r="BB279" s="7">
+      <c r="BB279" s="14">
         <f>SUM(BB6:BB278)</f>
         <v/>
       </c>
-      <c r="BC279" s="7">
+      <c r="BC279" s="14">
         <f>SUM(BC6:BC278)</f>
         <v/>
       </c>
-      <c r="BD279" s="7">
+      <c r="BD279" s="14">
         <f>SUM(BD6:BD278)</f>
         <v/>
       </c>
-      <c r="BE279" s="7">
+      <c r="BE279" s="14">
         <f>SUM(BE6:BE278)</f>
         <v/>
       </c>
-      <c r="BF279" s="7">
+      <c r="BF279" s="14">
         <f>SUM(BF6:BF278)</f>
         <v/>
       </c>
-      <c r="BG279" s="7">
+      <c r="BG279" s="14">
         <f>SUM(BG6:BG278)</f>
         <v/>
       </c>
-      <c r="BH279" s="7">
+      <c r="BH279" s="14">
         <f>SUM(BH6:BH278)</f>
         <v/>
       </c>
-      <c r="BI279" s="7">
+      <c r="BI279" s="14">
         <f>SUM(BI6:BI278)</f>
         <v/>
       </c>
-      <c r="BJ279" s="7">
+      <c r="BJ279" s="14">
         <f>SUM(BJ6:BJ278)</f>
         <v/>
       </c>
-      <c r="BK279" s="7">
+      <c r="BK279" s="14">
         <f>SUM(BK6:BK278)</f>
         <v/>
       </c>
-      <c r="BL279" s="7">
+      <c r="BL279" s="14">
         <f>SUM(BL6:BL278)</f>
         <v/>
       </c>
-      <c r="BM279" s="7">
+      <c r="BM279" s="14">
         <f>SUM(BM6:BM278)</f>
         <v/>
       </c>
-      <c r="BN279" s="7">
+      <c r="BN279" s="14">
         <f>SUM(BN6:BN278)</f>
         <v/>
       </c>
-      <c r="BO279" s="7">
+      <c r="BO279" s="14">
         <f>SUM(BO6:BO278)</f>
         <v/>
       </c>
-      <c r="BP279" s="7">
+      <c r="BP279" s="14">
         <f>SUM(BP6:BP278)</f>
         <v/>
       </c>
-      <c r="BQ279" s="7">
+      <c r="BQ279" s="14">
         <f>SUM(BQ6:BQ278)</f>
         <v/>
       </c>
-      <c r="BR279" s="7">
+      <c r="BR279" s="14">
         <f>SUM(BR6:BR278)</f>
         <v/>
       </c>
-      <c r="BS279" s="7">
+      <c r="BS279" s="14">
         <f>SUM(BS6:BS278)</f>
         <v/>
       </c>
-      <c r="BT279" s="7">
+      <c r="BT279" s="14">
         <f>SUM(BT6:BT278)</f>
         <v/>
       </c>
-      <c r="BU279" s="7">
+      <c r="BU279" s="14">
         <f>SUM(BU6:BU278)</f>
         <v/>
       </c>
-      <c r="BV279" s="7">
+      <c r="BV279" s="14">
         <f>SUM(BV6:BV278)</f>
         <v/>
       </c>
-      <c r="BW279" s="7">
+      <c r="BW279" s="14">
         <f>SUM(BW6:BW278)</f>
+        <v/>
+      </c>
+      <c r="BX279" s="14">
+        <f>SUM(BX6:BX278)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="9" t="inlineStr">
+        <is>
+          <t>POSTAL BALLOT VOTES</t>
+        </is>
+      </c>
+      <c r="B280" s="10" t="inlineStr"/>
+      <c r="C280" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D280" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E280" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F280" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G280" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H280" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I280" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J280" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K280" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L280" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M280" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N280" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O280" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P280" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q280" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R280" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S280" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T280" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U280" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V280" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W280" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X280" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y280" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z280" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA280" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB280" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC280" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD280" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE280" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF280" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG280" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH280" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI280" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ280" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK280" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL280" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM280" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN280" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO280" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP280" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ280" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR280" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS280" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT280" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU280" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV280" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW280" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX280" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY280" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ280" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA280" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB280" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC280" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD280" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE280" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF280" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG280" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH280" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI280" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ280" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK280" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL280" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM280" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN280" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO280" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP280" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ280" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR280" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS280" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT280" s="10" t="n">
+        <v>134</v>
+      </c>
+      <c r="BU280" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="BV280" s="10" t="n">
+        <v>145</v>
+      </c>
+      <c r="BW280" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX280" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="11" t="inlineStr">
+        <is>
+          <t>TOTAL VOTES POLLED</t>
+        </is>
+      </c>
+      <c r="B281" s="12" t="inlineStr"/>
+      <c r="C281" s="12">
+        <f>C279+C280</f>
+        <v/>
+      </c>
+      <c r="D281" s="12">
+        <f>D279+D280</f>
+        <v/>
+      </c>
+      <c r="E281" s="12">
+        <f>E279+E280</f>
+        <v/>
+      </c>
+      <c r="F281" s="12">
+        <f>F279+F280</f>
+        <v/>
+      </c>
+      <c r="G281" s="12">
+        <f>G279+G280</f>
+        <v/>
+      </c>
+      <c r="H281" s="12">
+        <f>H279+H280</f>
+        <v/>
+      </c>
+      <c r="I281" s="12">
+        <f>I279+I280</f>
+        <v/>
+      </c>
+      <c r="J281" s="12">
+        <f>J279+J280</f>
+        <v/>
+      </c>
+      <c r="K281" s="12">
+        <f>K279+K280</f>
+        <v/>
+      </c>
+      <c r="L281" s="12">
+        <f>L279+L280</f>
+        <v/>
+      </c>
+      <c r="M281" s="12">
+        <f>M279+M280</f>
+        <v/>
+      </c>
+      <c r="N281" s="12">
+        <f>N279+N280</f>
+        <v/>
+      </c>
+      <c r="O281" s="12">
+        <f>O279+O280</f>
+        <v/>
+      </c>
+      <c r="P281" s="12">
+        <f>P279+P280</f>
+        <v/>
+      </c>
+      <c r="Q281" s="12">
+        <f>Q279+Q280</f>
+        <v/>
+      </c>
+      <c r="R281" s="12">
+        <f>R279+R280</f>
+        <v/>
+      </c>
+      <c r="S281" s="12">
+        <f>S279+S280</f>
+        <v/>
+      </c>
+      <c r="T281" s="12">
+        <f>T279+T280</f>
+        <v/>
+      </c>
+      <c r="U281" s="12">
+        <f>U279+U280</f>
+        <v/>
+      </c>
+      <c r="V281" s="12">
+        <f>V279+V280</f>
+        <v/>
+      </c>
+      <c r="W281" s="12">
+        <f>W279+W280</f>
+        <v/>
+      </c>
+      <c r="X281" s="12">
+        <f>X279+X280</f>
+        <v/>
+      </c>
+      <c r="Y281" s="12">
+        <f>Y279+Y280</f>
+        <v/>
+      </c>
+      <c r="Z281" s="12">
+        <f>Z279+Z280</f>
+        <v/>
+      </c>
+      <c r="AA281" s="12">
+        <f>AA279+AA280</f>
+        <v/>
+      </c>
+      <c r="AB281" s="12">
+        <f>AB279+AB280</f>
+        <v/>
+      </c>
+      <c r="AC281" s="12">
+        <f>AC279+AC280</f>
+        <v/>
+      </c>
+      <c r="AD281" s="12">
+        <f>AD279+AD280</f>
+        <v/>
+      </c>
+      <c r="AE281" s="12">
+        <f>AE279+AE280</f>
+        <v/>
+      </c>
+      <c r="AF281" s="12">
+        <f>AF279+AF280</f>
+        <v/>
+      </c>
+      <c r="AG281" s="12">
+        <f>AG279+AG280</f>
+        <v/>
+      </c>
+      <c r="AH281" s="12">
+        <f>AH279+AH280</f>
+        <v/>
+      </c>
+      <c r="AI281" s="12">
+        <f>AI279+AI280</f>
+        <v/>
+      </c>
+      <c r="AJ281" s="12">
+        <f>AJ279+AJ280</f>
+        <v/>
+      </c>
+      <c r="AK281" s="12">
+        <f>AK279+AK280</f>
+        <v/>
+      </c>
+      <c r="AL281" s="12">
+        <f>AL279+AL280</f>
+        <v/>
+      </c>
+      <c r="AM281" s="12">
+        <f>AM279+AM280</f>
+        <v/>
+      </c>
+      <c r="AN281" s="12">
+        <f>AN279+AN280</f>
+        <v/>
+      </c>
+      <c r="AO281" s="12">
+        <f>AO279+AO280</f>
+        <v/>
+      </c>
+      <c r="AP281" s="12">
+        <f>AP279+AP280</f>
+        <v/>
+      </c>
+      <c r="AQ281" s="12">
+        <f>AQ279+AQ280</f>
+        <v/>
+      </c>
+      <c r="AR281" s="12">
+        <f>AR279+AR280</f>
+        <v/>
+      </c>
+      <c r="AS281" s="12">
+        <f>AS279+AS280</f>
+        <v/>
+      </c>
+      <c r="AT281" s="12">
+        <f>AT279+AT280</f>
+        <v/>
+      </c>
+      <c r="AU281" s="12">
+        <f>AU279+AU280</f>
+        <v/>
+      </c>
+      <c r="AV281" s="12">
+        <f>AV279+AV280</f>
+        <v/>
+      </c>
+      <c r="AW281" s="12">
+        <f>AW279+AW280</f>
+        <v/>
+      </c>
+      <c r="AX281" s="12">
+        <f>AX279+AX280</f>
+        <v/>
+      </c>
+      <c r="AY281" s="12">
+        <f>AY279+AY280</f>
+        <v/>
+      </c>
+      <c r="AZ281" s="12">
+        <f>AZ279+AZ280</f>
+        <v/>
+      </c>
+      <c r="BA281" s="12">
+        <f>BA279+BA280</f>
+        <v/>
+      </c>
+      <c r="BB281" s="12">
+        <f>BB279+BB280</f>
+        <v/>
+      </c>
+      <c r="BC281" s="12">
+        <f>BC279+BC280</f>
+        <v/>
+      </c>
+      <c r="BD281" s="12">
+        <f>BD279+BD280</f>
+        <v/>
+      </c>
+      <c r="BE281" s="12">
+        <f>BE279+BE280</f>
+        <v/>
+      </c>
+      <c r="BF281" s="12">
+        <f>BF279+BF280</f>
+        <v/>
+      </c>
+      <c r="BG281" s="12">
+        <f>BG279+BG280</f>
+        <v/>
+      </c>
+      <c r="BH281" s="12">
+        <f>BH279+BH280</f>
+        <v/>
+      </c>
+      <c r="BI281" s="12">
+        <f>BI279+BI280</f>
+        <v/>
+      </c>
+      <c r="BJ281" s="12">
+        <f>BJ279+BJ280</f>
+        <v/>
+      </c>
+      <c r="BK281" s="12">
+        <f>BK279+BK280</f>
+        <v/>
+      </c>
+      <c r="BL281" s="12">
+        <f>BL279+BL280</f>
+        <v/>
+      </c>
+      <c r="BM281" s="12">
+        <f>BM279+BM280</f>
+        <v/>
+      </c>
+      <c r="BN281" s="12">
+        <f>BN279+BN280</f>
+        <v/>
+      </c>
+      <c r="BO281" s="12">
+        <f>BO279+BO280</f>
+        <v/>
+      </c>
+      <c r="BP281" s="12">
+        <f>BP279+BP280</f>
+        <v/>
+      </c>
+      <c r="BQ281" s="12">
+        <f>BQ279+BQ280</f>
+        <v/>
+      </c>
+      <c r="BR281" s="12">
+        <f>BR279+BR280</f>
+        <v/>
+      </c>
+      <c r="BS281" s="12">
+        <f>BS279+BS280</f>
+        <v/>
+      </c>
+      <c r="BT281" s="12">
+        <f>BT279+BT280</f>
+        <v/>
+      </c>
+      <c r="BU281" s="12">
+        <f>BU279+BU280</f>
+        <v/>
+      </c>
+      <c r="BV281" s="12">
+        <f>BV279+BV280</f>
+        <v/>
+      </c>
+      <c r="BW281" s="12">
+        <f>BW279+BW280</f>
+        <v/>
+      </c>
+      <c r="BX281" s="12">
+        <f>BX279+BX280</f>
         <v/>
       </c>
     </row>

--- a/AC_2010Bye/AC_031_Huzurabad.xlsx
+++ b/AC_2010Bye/AC_031_Huzurabad.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,6 +50,11 @@
       <b val="1"/>
       <color rgb="00000000"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="6">
@@ -84,7 +89,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -148,11 +153,19 @@
         <color rgb="001B365D"/>
       </bottom>
     </border>
+    <border>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="double">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -180,6 +193,25 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -649,7 +681,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
@@ -64398,839 +64429,839 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="8" t="inlineStr">
+      <c r="A279" s="15" t="inlineStr">
         <is>
           <t>TOTAL EVM VOTES</t>
         </is>
       </c>
-      <c r="B279" s="13" t="inlineStr"/>
-      <c r="C279" s="14">
+      <c r="B279" s="16" t="inlineStr"/>
+      <c r="C279" s="17">
         <f>SUM(C6:C278)</f>
         <v/>
       </c>
-      <c r="D279" s="14">
+      <c r="D279" s="17">
         <f>SUM(D6:D278)</f>
         <v/>
       </c>
-      <c r="E279" s="14">
+      <c r="E279" s="17">
         <f>SUM(E6:E278)</f>
         <v/>
       </c>
-      <c r="F279" s="14">
+      <c r="F279" s="17">
         <f>SUM(F6:F278)</f>
         <v/>
       </c>
-      <c r="G279" s="14">
+      <c r="G279" s="17">
         <f>SUM(G6:G278)</f>
         <v/>
       </c>
-      <c r="H279" s="14">
+      <c r="H279" s="17">
         <f>SUM(H6:H278)</f>
         <v/>
       </c>
-      <c r="I279" s="14">
+      <c r="I279" s="17">
         <f>SUM(I6:I278)</f>
         <v/>
       </c>
-      <c r="J279" s="14">
+      <c r="J279" s="17">
         <f>SUM(J6:J278)</f>
         <v/>
       </c>
-      <c r="K279" s="14">
+      <c r="K279" s="17">
         <f>SUM(K6:K278)</f>
         <v/>
       </c>
-      <c r="L279" s="14">
+      <c r="L279" s="17">
         <f>SUM(L6:L278)</f>
         <v/>
       </c>
-      <c r="M279" s="14">
+      <c r="M279" s="17">
         <f>SUM(M6:M278)</f>
         <v/>
       </c>
-      <c r="N279" s="14">
+      <c r="N279" s="17">
         <f>SUM(N6:N278)</f>
         <v/>
       </c>
-      <c r="O279" s="14">
+      <c r="O279" s="17">
         <f>SUM(O6:O278)</f>
         <v/>
       </c>
-      <c r="P279" s="14">
+      <c r="P279" s="17">
         <f>SUM(P6:P278)</f>
         <v/>
       </c>
-      <c r="Q279" s="14">
+      <c r="Q279" s="17">
         <f>SUM(Q6:Q278)</f>
         <v/>
       </c>
-      <c r="R279" s="14">
+      <c r="R279" s="17">
         <f>SUM(R6:R278)</f>
         <v/>
       </c>
-      <c r="S279" s="14">
+      <c r="S279" s="17">
         <f>SUM(S6:S278)</f>
         <v/>
       </c>
-      <c r="T279" s="14">
+      <c r="T279" s="17">
         <f>SUM(T6:T278)</f>
         <v/>
       </c>
-      <c r="U279" s="14">
+      <c r="U279" s="17">
         <f>SUM(U6:U278)</f>
         <v/>
       </c>
-      <c r="V279" s="14">
+      <c r="V279" s="17">
         <f>SUM(V6:V278)</f>
         <v/>
       </c>
-      <c r="W279" s="14">
+      <c r="W279" s="17">
         <f>SUM(W6:W278)</f>
         <v/>
       </c>
-      <c r="X279" s="14">
+      <c r="X279" s="17">
         <f>SUM(X6:X278)</f>
         <v/>
       </c>
-      <c r="Y279" s="14">
+      <c r="Y279" s="17">
         <f>SUM(Y6:Y278)</f>
         <v/>
       </c>
-      <c r="Z279" s="14">
+      <c r="Z279" s="17">
         <f>SUM(Z6:Z278)</f>
         <v/>
       </c>
-      <c r="AA279" s="14">
+      <c r="AA279" s="17">
         <f>SUM(AA6:AA278)</f>
         <v/>
       </c>
-      <c r="AB279" s="14">
+      <c r="AB279" s="17">
         <f>SUM(AB6:AB278)</f>
         <v/>
       </c>
-      <c r="AC279" s="14">
+      <c r="AC279" s="17">
         <f>SUM(AC6:AC278)</f>
         <v/>
       </c>
-      <c r="AD279" s="14">
+      <c r="AD279" s="17">
         <f>SUM(AD6:AD278)</f>
         <v/>
       </c>
-      <c r="AE279" s="14">
+      <c r="AE279" s="17">
         <f>SUM(AE6:AE278)</f>
         <v/>
       </c>
-      <c r="AF279" s="14">
+      <c r="AF279" s="17">
         <f>SUM(AF6:AF278)</f>
         <v/>
       </c>
-      <c r="AG279" s="14">
+      <c r="AG279" s="17">
         <f>SUM(AG6:AG278)</f>
         <v/>
       </c>
-      <c r="AH279" s="14">
+      <c r="AH279" s="17">
         <f>SUM(AH6:AH278)</f>
         <v/>
       </c>
-      <c r="AI279" s="14">
+      <c r="AI279" s="17">
         <f>SUM(AI6:AI278)</f>
         <v/>
       </c>
-      <c r="AJ279" s="14">
+      <c r="AJ279" s="17">
         <f>SUM(AJ6:AJ278)</f>
         <v/>
       </c>
-      <c r="AK279" s="14">
+      <c r="AK279" s="17">
         <f>SUM(AK6:AK278)</f>
         <v/>
       </c>
-      <c r="AL279" s="14">
+      <c r="AL279" s="17">
         <f>SUM(AL6:AL278)</f>
         <v/>
       </c>
-      <c r="AM279" s="14">
+      <c r="AM279" s="17">
         <f>SUM(AM6:AM278)</f>
         <v/>
       </c>
-      <c r="AN279" s="14">
+      <c r="AN279" s="17">
         <f>SUM(AN6:AN278)</f>
         <v/>
       </c>
-      <c r="AO279" s="14">
+      <c r="AO279" s="17">
         <f>SUM(AO6:AO278)</f>
         <v/>
       </c>
-      <c r="AP279" s="14">
+      <c r="AP279" s="17">
         <f>SUM(AP6:AP278)</f>
         <v/>
       </c>
-      <c r="AQ279" s="14">
+      <c r="AQ279" s="17">
         <f>SUM(AQ6:AQ278)</f>
         <v/>
       </c>
-      <c r="AR279" s="14">
+      <c r="AR279" s="17">
         <f>SUM(AR6:AR278)</f>
         <v/>
       </c>
-      <c r="AS279" s="14">
+      <c r="AS279" s="17">
         <f>SUM(AS6:AS278)</f>
         <v/>
       </c>
-      <c r="AT279" s="14">
+      <c r="AT279" s="17">
         <f>SUM(AT6:AT278)</f>
         <v/>
       </c>
-      <c r="AU279" s="14">
+      <c r="AU279" s="17">
         <f>SUM(AU6:AU278)</f>
         <v/>
       </c>
-      <c r="AV279" s="14">
+      <c r="AV279" s="17">
         <f>SUM(AV6:AV278)</f>
         <v/>
       </c>
-      <c r="AW279" s="14">
+      <c r="AW279" s="17">
         <f>SUM(AW6:AW278)</f>
         <v/>
       </c>
-      <c r="AX279" s="14">
+      <c r="AX279" s="17">
         <f>SUM(AX6:AX278)</f>
         <v/>
       </c>
-      <c r="AY279" s="14">
+      <c r="AY279" s="17">
         <f>SUM(AY6:AY278)</f>
         <v/>
       </c>
-      <c r="AZ279" s="14">
+      <c r="AZ279" s="17">
         <f>SUM(AZ6:AZ278)</f>
         <v/>
       </c>
-      <c r="BA279" s="14">
+      <c r="BA279" s="17">
         <f>SUM(BA6:BA278)</f>
         <v/>
       </c>
-      <c r="BB279" s="14">
+      <c r="BB279" s="17">
         <f>SUM(BB6:BB278)</f>
         <v/>
       </c>
-      <c r="BC279" s="14">
+      <c r="BC279" s="17">
         <f>SUM(BC6:BC278)</f>
         <v/>
       </c>
-      <c r="BD279" s="14">
+      <c r="BD279" s="17">
         <f>SUM(BD6:BD278)</f>
         <v/>
       </c>
-      <c r="BE279" s="14">
+      <c r="BE279" s="17">
         <f>SUM(BE6:BE278)</f>
         <v/>
       </c>
-      <c r="BF279" s="14">
+      <c r="BF279" s="17">
         <f>SUM(BF6:BF278)</f>
         <v/>
       </c>
-      <c r="BG279" s="14">
+      <c r="BG279" s="17">
         <f>SUM(BG6:BG278)</f>
         <v/>
       </c>
-      <c r="BH279" s="14">
+      <c r="BH279" s="17">
         <f>SUM(BH6:BH278)</f>
         <v/>
       </c>
-      <c r="BI279" s="14">
+      <c r="BI279" s="17">
         <f>SUM(BI6:BI278)</f>
         <v/>
       </c>
-      <c r="BJ279" s="14">
+      <c r="BJ279" s="17">
         <f>SUM(BJ6:BJ278)</f>
         <v/>
       </c>
-      <c r="BK279" s="14">
+      <c r="BK279" s="17">
         <f>SUM(BK6:BK278)</f>
         <v/>
       </c>
-      <c r="BL279" s="14">
+      <c r="BL279" s="17">
         <f>SUM(BL6:BL278)</f>
         <v/>
       </c>
-      <c r="BM279" s="14">
+      <c r="BM279" s="17">
         <f>SUM(BM6:BM278)</f>
         <v/>
       </c>
-      <c r="BN279" s="14">
+      <c r="BN279" s="17">
         <f>SUM(BN6:BN278)</f>
         <v/>
       </c>
-      <c r="BO279" s="14">
+      <c r="BO279" s="17">
         <f>SUM(BO6:BO278)</f>
         <v/>
       </c>
-      <c r="BP279" s="14">
+      <c r="BP279" s="17">
         <f>SUM(BP6:BP278)</f>
         <v/>
       </c>
-      <c r="BQ279" s="14">
+      <c r="BQ279" s="17">
         <f>SUM(BQ6:BQ278)</f>
         <v/>
       </c>
-      <c r="BR279" s="14">
+      <c r="BR279" s="17">
         <f>SUM(BR6:BR278)</f>
         <v/>
       </c>
-      <c r="BS279" s="14">
+      <c r="BS279" s="17">
         <f>SUM(BS6:BS278)</f>
         <v/>
       </c>
-      <c r="BT279" s="14">
+      <c r="BT279" s="17">
         <f>SUM(BT6:BT278)</f>
         <v/>
       </c>
-      <c r="BU279" s="14">
+      <c r="BU279" s="17">
         <f>SUM(BU6:BU278)</f>
         <v/>
       </c>
-      <c r="BV279" s="14">
+      <c r="BV279" s="17">
         <f>SUM(BV6:BV278)</f>
         <v/>
       </c>
-      <c r="BW279" s="14">
+      <c r="BW279" s="17">
         <f>SUM(BW6:BW278)</f>
         <v/>
       </c>
-      <c r="BX279" s="14">
+      <c r="BX279" s="17">
         <f>SUM(BX6:BX278)</f>
         <v/>
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="9" t="inlineStr">
+      <c r="A280" s="18" t="inlineStr">
         <is>
           <t>POSTAL BALLOT VOTES</t>
         </is>
       </c>
       <c r="B280" s="10" t="inlineStr"/>
-      <c r="C280" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D280" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E280" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F280" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G280" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H280" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I280" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J280" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K280" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L280" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M280" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N280" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O280" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P280" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q280" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R280" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S280" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T280" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U280" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V280" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W280" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X280" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y280" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z280" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA280" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB280" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC280" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD280" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE280" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF280" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG280" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH280" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI280" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ280" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK280" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL280" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM280" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN280" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO280" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP280" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ280" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR280" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS280" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT280" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU280" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV280" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW280" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX280" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY280" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ280" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA280" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB280" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC280" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD280" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE280" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF280" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG280" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH280" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI280" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ280" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK280" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL280" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM280" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN280" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO280" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP280" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ280" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR280" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS280" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT280" s="10" t="n">
+      <c r="C280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT280" s="17" t="n">
         <v>134</v>
       </c>
-      <c r="BU280" s="10" t="n">
+      <c r="BU280" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="BV280" s="10" t="n">
+      <c r="BV280" s="17" t="n">
         <v>145</v>
       </c>
-      <c r="BW280" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX280" s="10" t="n">
+      <c r="BW280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX280" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="11" t="inlineStr">
+      <c r="A281" s="19" t="inlineStr">
         <is>
           <t>TOTAL VOTES POLLED</t>
         </is>
       </c>
-      <c r="B281" s="12" t="inlineStr"/>
-      <c r="C281" s="12">
+      <c r="B281" s="20" t="inlineStr"/>
+      <c r="C281" s="21">
         <f>C279+C280</f>
         <v/>
       </c>
-      <c r="D281" s="12">
+      <c r="D281" s="21">
         <f>D279+D280</f>
         <v/>
       </c>
-      <c r="E281" s="12">
+      <c r="E281" s="21">
         <f>E279+E280</f>
         <v/>
       </c>
-      <c r="F281" s="12">
+      <c r="F281" s="21">
         <f>F279+F280</f>
         <v/>
       </c>
-      <c r="G281" s="12">
+      <c r="G281" s="21">
         <f>G279+G280</f>
         <v/>
       </c>
-      <c r="H281" s="12">
+      <c r="H281" s="21">
         <f>H279+H280</f>
         <v/>
       </c>
-      <c r="I281" s="12">
+      <c r="I281" s="21">
         <f>I279+I280</f>
         <v/>
       </c>
-      <c r="J281" s="12">
+      <c r="J281" s="21">
         <f>J279+J280</f>
         <v/>
       </c>
-      <c r="K281" s="12">
+      <c r="K281" s="21">
         <f>K279+K280</f>
         <v/>
       </c>
-      <c r="L281" s="12">
+      <c r="L281" s="21">
         <f>L279+L280</f>
         <v/>
       </c>
-      <c r="M281" s="12">
+      <c r="M281" s="21">
         <f>M279+M280</f>
         <v/>
       </c>
-      <c r="N281" s="12">
+      <c r="N281" s="21">
         <f>N279+N280</f>
         <v/>
       </c>
-      <c r="O281" s="12">
+      <c r="O281" s="21">
         <f>O279+O280</f>
         <v/>
       </c>
-      <c r="P281" s="12">
+      <c r="P281" s="21">
         <f>P279+P280</f>
         <v/>
       </c>
-      <c r="Q281" s="12">
+      <c r="Q281" s="21">
         <f>Q279+Q280</f>
         <v/>
       </c>
-      <c r="R281" s="12">
+      <c r="R281" s="21">
         <f>R279+R280</f>
         <v/>
       </c>
-      <c r="S281" s="12">
+      <c r="S281" s="21">
         <f>S279+S280</f>
         <v/>
       </c>
-      <c r="T281" s="12">
+      <c r="T281" s="21">
         <f>T279+T280</f>
         <v/>
       </c>
-      <c r="U281" s="12">
+      <c r="U281" s="21">
         <f>U279+U280</f>
         <v/>
       </c>
-      <c r="V281" s="12">
+      <c r="V281" s="21">
         <f>V279+V280</f>
         <v/>
       </c>
-      <c r="W281" s="12">
+      <c r="W281" s="21">
         <f>W279+W280</f>
         <v/>
       </c>
-      <c r="X281" s="12">
+      <c r="X281" s="21">
         <f>X279+X280</f>
         <v/>
       </c>
-      <c r="Y281" s="12">
+      <c r="Y281" s="21">
         <f>Y279+Y280</f>
         <v/>
       </c>
-      <c r="Z281" s="12">
+      <c r="Z281" s="21">
         <f>Z279+Z280</f>
         <v/>
       </c>
-      <c r="AA281" s="12">
+      <c r="AA281" s="21">
         <f>AA279+AA280</f>
         <v/>
       </c>
-      <c r="AB281" s="12">
+      <c r="AB281" s="21">
         <f>AB279+AB280</f>
         <v/>
       </c>
-      <c r="AC281" s="12">
+      <c r="AC281" s="21">
         <f>AC279+AC280</f>
         <v/>
       </c>
-      <c r="AD281" s="12">
+      <c r="AD281" s="21">
         <f>AD279+AD280</f>
         <v/>
       </c>
-      <c r="AE281" s="12">
+      <c r="AE281" s="21">
         <f>AE279+AE280</f>
         <v/>
       </c>
-      <c r="AF281" s="12">
+      <c r="AF281" s="21">
         <f>AF279+AF280</f>
         <v/>
       </c>
-      <c r="AG281" s="12">
+      <c r="AG281" s="21">
         <f>AG279+AG280</f>
         <v/>
       </c>
-      <c r="AH281" s="12">
+      <c r="AH281" s="21">
         <f>AH279+AH280</f>
         <v/>
       </c>
-      <c r="AI281" s="12">
+      <c r="AI281" s="21">
         <f>AI279+AI280</f>
         <v/>
       </c>
-      <c r="AJ281" s="12">
+      <c r="AJ281" s="21">
         <f>AJ279+AJ280</f>
         <v/>
       </c>
-      <c r="AK281" s="12">
+      <c r="AK281" s="21">
         <f>AK279+AK280</f>
         <v/>
       </c>
-      <c r="AL281" s="12">
+      <c r="AL281" s="21">
         <f>AL279+AL280</f>
         <v/>
       </c>
-      <c r="AM281" s="12">
+      <c r="AM281" s="21">
         <f>AM279+AM280</f>
         <v/>
       </c>
-      <c r="AN281" s="12">
+      <c r="AN281" s="21">
         <f>AN279+AN280</f>
         <v/>
       </c>
-      <c r="AO281" s="12">
+      <c r="AO281" s="21">
         <f>AO279+AO280</f>
         <v/>
       </c>
-      <c r="AP281" s="12">
+      <c r="AP281" s="21">
         <f>AP279+AP280</f>
         <v/>
       </c>
-      <c r="AQ281" s="12">
+      <c r="AQ281" s="21">
         <f>AQ279+AQ280</f>
         <v/>
       </c>
-      <c r="AR281" s="12">
+      <c r="AR281" s="21">
         <f>AR279+AR280</f>
         <v/>
       </c>
-      <c r="AS281" s="12">
+      <c r="AS281" s="21">
         <f>AS279+AS280</f>
         <v/>
       </c>
-      <c r="AT281" s="12">
+      <c r="AT281" s="21">
         <f>AT279+AT280</f>
         <v/>
       </c>
-      <c r="AU281" s="12">
+      <c r="AU281" s="21">
         <f>AU279+AU280</f>
         <v/>
       </c>
-      <c r="AV281" s="12">
+      <c r="AV281" s="21">
         <f>AV279+AV280</f>
         <v/>
       </c>
-      <c r="AW281" s="12">
+      <c r="AW281" s="21">
         <f>AW279+AW280</f>
         <v/>
       </c>
-      <c r="AX281" s="12">
+      <c r="AX281" s="21">
         <f>AX279+AX280</f>
         <v/>
       </c>
-      <c r="AY281" s="12">
+      <c r="AY281" s="21">
         <f>AY279+AY280</f>
         <v/>
       </c>
-      <c r="AZ281" s="12">
+      <c r="AZ281" s="21">
         <f>AZ279+AZ280</f>
         <v/>
       </c>
-      <c r="BA281" s="12">
+      <c r="BA281" s="21">
         <f>BA279+BA280</f>
         <v/>
       </c>
-      <c r="BB281" s="12">
+      <c r="BB281" s="21">
         <f>BB279+BB280</f>
         <v/>
       </c>
-      <c r="BC281" s="12">
+      <c r="BC281" s="21">
         <f>BC279+BC280</f>
         <v/>
       </c>
-      <c r="BD281" s="12">
+      <c r="BD281" s="21">
         <f>BD279+BD280</f>
         <v/>
       </c>
-      <c r="BE281" s="12">
+      <c r="BE281" s="21">
         <f>BE279+BE280</f>
         <v/>
       </c>
-      <c r="BF281" s="12">
+      <c r="BF281" s="21">
         <f>BF279+BF280</f>
         <v/>
       </c>
-      <c r="BG281" s="12">
+      <c r="BG281" s="21">
         <f>BG279+BG280</f>
         <v/>
       </c>
-      <c r="BH281" s="12">
+      <c r="BH281" s="21">
         <f>BH279+BH280</f>
         <v/>
       </c>
-      <c r="BI281" s="12">
+      <c r="BI281" s="21">
         <f>BI279+BI280</f>
         <v/>
       </c>
-      <c r="BJ281" s="12">
+      <c r="BJ281" s="21">
         <f>BJ279+BJ280</f>
         <v/>
       </c>
-      <c r="BK281" s="12">
+      <c r="BK281" s="21">
         <f>BK279+BK280</f>
         <v/>
       </c>
-      <c r="BL281" s="12">
+      <c r="BL281" s="21">
         <f>BL279+BL280</f>
         <v/>
       </c>
-      <c r="BM281" s="12">
+      <c r="BM281" s="21">
         <f>BM279+BM280</f>
         <v/>
       </c>
-      <c r="BN281" s="12">
+      <c r="BN281" s="21">
         <f>BN279+BN280</f>
         <v/>
       </c>
-      <c r="BO281" s="12">
+      <c r="BO281" s="21">
         <f>BO279+BO280</f>
         <v/>
       </c>
-      <c r="BP281" s="12">
+      <c r="BP281" s="21">
         <f>BP279+BP280</f>
         <v/>
       </c>
-      <c r="BQ281" s="12">
+      <c r="BQ281" s="21">
         <f>BQ279+BQ280</f>
         <v/>
       </c>
-      <c r="BR281" s="12">
+      <c r="BR281" s="21">
         <f>BR279+BR280</f>
         <v/>
       </c>
-      <c r="BS281" s="12">
+      <c r="BS281" s="21">
         <f>BS279+BS280</f>
         <v/>
       </c>
-      <c r="BT281" s="12">
+      <c r="BT281" s="21">
         <f>BT279+BT280</f>
         <v/>
       </c>
-      <c r="BU281" s="12">
+      <c r="BU281" s="21">
         <f>BU279+BU280</f>
         <v/>
       </c>
-      <c r="BV281" s="12">
+      <c r="BV281" s="21">
         <f>BV279+BV280</f>
         <v/>
       </c>
-      <c r="BW281" s="12">
+      <c r="BW281" s="21">
         <f>BW279+BW280</f>
         <v/>
       </c>
-      <c r="BX281" s="12">
+      <c r="BX281" s="21">
         <f>BX279+BX280</f>
         <v/>
       </c>
